--- a/2026年10月_出勤表.xlsx
+++ b/2026年10月_出勤表.xlsx
@@ -554,12 +554,12 @@
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
+          <t>山谷大地</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
           <t>横山凌</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>山谷大地</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
@@ -625,22 +625,26 @@
           <t>休</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>②</t>
         </is>
       </c>
-      <c r="K3" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="L3" s="5" t="n"/>
+      <c r="L3" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
       <c r="M3" s="5" t="n"/>
     </row>
     <row r="4">
@@ -655,9 +659,9 @@
       <c r="C4" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>①</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
@@ -670,32 +674,36 @@
           <t>③</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>④</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>①</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
         <is>
           <t>③</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>④</t>
-        </is>
-      </c>
-      <c r="L4" s="5" t="n"/>
       <c r="M4" s="5" t="n"/>
     </row>
     <row r="5">
@@ -715,9 +723,9 @@
           <t>①</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>②</t>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
@@ -732,25 +740,29 @@
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="J5" s="8" t="inlineStr">
+        <is>
+          <t>③</t>
+        </is>
+      </c>
+      <c r="K5" s="8" t="inlineStr">
+        <is>
+          <t>④</t>
+        </is>
+      </c>
+      <c r="L5" s="8" t="inlineStr">
+        <is>
           <t>①</t>
         </is>
       </c>
-      <c r="I5" s="8" t="inlineStr">
-        <is>
-          <t>④</t>
-        </is>
-      </c>
-      <c r="J5" s="8" t="inlineStr">
-        <is>
-          <t>③</t>
-        </is>
-      </c>
-      <c r="K5" s="8" t="inlineStr">
-        <is>
-          <t>②</t>
-        </is>
-      </c>
-      <c r="L5" s="5" t="n"/>
       <c r="M5" s="5" t="n"/>
     </row>
     <row r="6">
@@ -765,9 +777,9 @@
       <c r="C6" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>①</t>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="E6" s="10" t="inlineStr">
@@ -787,25 +799,29 @@
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
           <t>④</t>
         </is>
       </c>
-      <c r="I6" s="10" t="inlineStr">
+      <c r="J6" s="10" t="inlineStr">
         <is>
           <t>②</t>
         </is>
       </c>
-      <c r="J6" s="10" t="inlineStr">
-        <is>
-          <t>①</t>
-        </is>
-      </c>
       <c r="K6" s="10" t="inlineStr">
         <is>
           <t>③</t>
         </is>
       </c>
-      <c r="L6" s="5" t="n"/>
+      <c r="L6" s="10" t="inlineStr">
+        <is>
+          <t>⑤</t>
+        </is>
+      </c>
       <c r="M6" s="5" t="n"/>
     </row>
     <row r="7">
@@ -825,14 +841,14 @@
           <t>休</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>③</t>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>②</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -840,14 +856,14 @@
           <t>④</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>③</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>②</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
@@ -855,12 +871,16 @@
           <t>休</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
         <is>
           <t>④</t>
         </is>
       </c>
-      <c r="L7" s="5" t="n"/>
       <c r="M7" s="5" t="n"/>
     </row>
     <row r="8">
@@ -880,9 +900,9 @@
           <t>①</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>②</t>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
@@ -890,9 +910,9 @@
           <t>休</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>④</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
@@ -900,22 +920,26 @@
           <t>休</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>④</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>②</t>
-        </is>
-      </c>
-      <c r="K8" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="L8" s="5" t="n"/>
+      <c r="L8" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
       <c r="M8" s="5" t="n"/>
     </row>
     <row r="9">
@@ -935,14 +959,14 @@
           <t>①</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>②</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>③</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
@@ -955,22 +979,26 @@
           <t>休</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>②</t>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
+          <t>③</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
           <t>①</t>
         </is>
       </c>
-      <c r="K9" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="L9" s="5" t="n"/>
+      <c r="L9" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
       <c r="M9" s="5" t="n"/>
     </row>
     <row r="10">
@@ -990,29 +1018,29 @@
           <t>休</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>③</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>④</t>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>②</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>④</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>⑤</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
@@ -1020,12 +1048,16 @@
           <t>休</t>
         </is>
       </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>③</t>
-        </is>
-      </c>
-      <c r="L10" s="5" t="n"/>
+      <c r="K10" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>②</t>
+        </is>
+      </c>
       <c r="M10" s="5" t="n"/>
     </row>
     <row r="11">
@@ -1045,29 +1077,29 @@
           <t>休</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>③</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>④</t>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>②</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>③</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>②</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
@@ -1075,12 +1107,16 @@
           <t>休</t>
         </is>
       </c>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>④</t>
-        </is>
-      </c>
-      <c r="L11" s="5" t="n"/>
+      <c r="K11" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>⑤</t>
+        </is>
+      </c>
       <c r="M11" s="5" t="n"/>
     </row>
     <row r="12">
@@ -1115,27 +1151,31 @@
           <t>④</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr">
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>③</t>
+        </is>
+      </c>
+      <c r="J12" s="8" t="inlineStr">
+        <is>
+          <t>①</t>
+        </is>
+      </c>
+      <c r="K12" s="8" t="inlineStr">
+        <is>
+          <t>④</t>
+        </is>
+      </c>
+      <c r="L12" s="8" t="inlineStr">
         <is>
           <t>②</t>
         </is>
       </c>
-      <c r="I12" s="8" t="inlineStr">
-        <is>
-          <t>③</t>
-        </is>
-      </c>
-      <c r="J12" s="8" t="inlineStr">
-        <is>
-          <t>④</t>
-        </is>
-      </c>
-      <c r="K12" s="8" t="inlineStr">
-        <is>
-          <t>①</t>
-        </is>
-      </c>
-      <c r="L12" s="5" t="n"/>
       <c r="M12" s="5" t="n"/>
     </row>
     <row r="13">
@@ -1165,32 +1205,36 @@
           <t>③</t>
         </is>
       </c>
-      <c r="G13" s="10" t="inlineStr">
-        <is>
-          <t>④</t>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>③</t>
+        </is>
+      </c>
+      <c r="J13" s="10" t="inlineStr">
+        <is>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="K13" s="10" t="inlineStr">
+        <is>
+          <t>②</t>
+        </is>
+      </c>
+      <c r="L13" s="10" t="inlineStr">
+        <is>
           <t>①</t>
         </is>
       </c>
-      <c r="I13" s="10" t="inlineStr">
-        <is>
-          <t>④</t>
-        </is>
-      </c>
-      <c r="J13" s="10" t="inlineStr">
-        <is>
-          <t>③</t>
-        </is>
-      </c>
-      <c r="K13" s="10" t="inlineStr">
-        <is>
-          <t>②</t>
-        </is>
-      </c>
-      <c r="L13" s="5" t="n"/>
       <c r="M13" s="5" t="n"/>
     </row>
     <row r="14">
@@ -1205,24 +1249,24 @@
       <c r="C14" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>①</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>②</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>③</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>④</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
@@ -1230,22 +1274,26 @@
           <t>休</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>①</t>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>②</t>
-        </is>
-      </c>
-      <c r="K14" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="L14" s="5" t="n"/>
+          <t>④</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>③</t>
+        </is>
+      </c>
+      <c r="L14" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
       <c r="M14" s="5" t="n"/>
     </row>
     <row r="15">
@@ -1265,9 +1313,9 @@
           <t>①</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>②</t>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -1275,9 +1323,9 @@
           <t>休</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>④</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
@@ -1285,22 +1333,26 @@
           <t>休</t>
         </is>
       </c>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>②</t>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
+          <t>④</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
           <t>①</t>
         </is>
       </c>
-      <c r="K15" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="L15" s="5" t="n"/>
+      <c r="L15" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
       <c r="M15" s="5" t="n"/>
     </row>
     <row r="16">
@@ -1325,9 +1377,9 @@
           <t>休</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>③</t>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -1337,25 +1389,29 @@
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
           <t>④</t>
         </is>
       </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
           <t>休</t>
         </is>
       </c>
-      <c r="K16" s="5" t="inlineStr">
-        <is>
-          <t>③</t>
-        </is>
-      </c>
-      <c r="L16" s="5" t="n"/>
+      <c r="K16" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>⑤</t>
+        </is>
+      </c>
       <c r="M16" s="5" t="n"/>
     </row>
     <row r="17">
@@ -1385,19 +1441,19 @@
           <t>③</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>④</t>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>④</t>
-        </is>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>⑤</t>
         </is>
       </c>
       <c r="J17" s="6" t="inlineStr">
@@ -1405,12 +1461,16 @@
           <t>休</t>
         </is>
       </c>
-      <c r="K17" s="5" t="inlineStr">
+      <c r="K17" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
         <is>
           <t>③</t>
         </is>
       </c>
-      <c r="L17" s="5" t="n"/>
       <c r="M17" s="5" t="n"/>
     </row>
     <row r="18">
@@ -1450,22 +1510,26 @@
           <t>休</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="J18" s="5" t="inlineStr">
+      <c r="K18" s="5" t="inlineStr">
         <is>
           <t>②</t>
         </is>
       </c>
-      <c r="K18" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="L18" s="5" t="n"/>
+      <c r="L18" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
       <c r="M18" s="5" t="n"/>
     </row>
     <row r="19">
@@ -1490,9 +1554,9 @@
           <t>②</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
-        <is>
-          <t>③</t>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="G19" s="8" t="inlineStr">
@@ -1502,25 +1566,29 @@
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="I19" s="8" t="inlineStr">
+        <is>
+          <t>①</t>
+        </is>
+      </c>
+      <c r="J19" s="8" t="inlineStr">
+        <is>
           <t>②</t>
         </is>
       </c>
-      <c r="I19" s="8" t="inlineStr">
-        <is>
-          <t>③</t>
-        </is>
-      </c>
-      <c r="J19" s="8" t="inlineStr">
+      <c r="K19" s="8" t="inlineStr">
+        <is>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="L19" s="8" t="inlineStr">
         <is>
           <t>④</t>
         </is>
       </c>
-      <c r="K19" s="8" t="inlineStr">
-        <is>
-          <t>①</t>
-        </is>
-      </c>
-      <c r="L19" s="5" t="n"/>
       <c r="M19" s="5" t="n"/>
     </row>
     <row r="20">
@@ -1555,27 +1623,31 @@
           <t>④</t>
         </is>
       </c>
-      <c r="H20" s="10" t="inlineStr">
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="I20" s="10" t="inlineStr">
         <is>
           <t>②</t>
         </is>
       </c>
-      <c r="I20" s="10" t="inlineStr">
+      <c r="J20" s="10" t="inlineStr">
         <is>
           <t>③</t>
         </is>
       </c>
-      <c r="J20" s="10" t="inlineStr">
+      <c r="K20" s="10" t="inlineStr">
         <is>
           <t>④</t>
         </is>
       </c>
-      <c r="K20" s="10" t="inlineStr">
+      <c r="L20" s="10" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="L20" s="5" t="n"/>
       <c r="M20" s="5" t="n"/>
     </row>
     <row r="21">
@@ -1590,19 +1662,19 @@
       <c r="C21" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>①</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>②</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>③</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
@@ -1610,27 +1682,31 @@
           <t>休</t>
         </is>
       </c>
-      <c r="H21" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="I21" s="5" t="inlineStr">
-        <is>
-          <t>②</t>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>①</t>
-        </is>
-      </c>
-      <c r="K21" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="L21" s="5" t="n"/>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>③</t>
+        </is>
+      </c>
+      <c r="L21" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
       <c r="M21" s="5" t="n"/>
     </row>
     <row r="22">
@@ -1660,32 +1736,36 @@
           <t>③</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>④</t>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="K22" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
           <t>③</t>
         </is>
       </c>
-      <c r="I22" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="J22" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="K22" s="5" t="inlineStr">
-        <is>
-          <t>④</t>
-        </is>
-      </c>
-      <c r="L22" s="5" t="n"/>
       <c r="M22" s="5" t="n"/>
     </row>
     <row r="23">
@@ -1700,34 +1780,34 @@
       <c r="C23" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>③</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>④</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>④</t>
-        </is>
-      </c>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>①</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>②</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>①</t>
         </is>
       </c>
       <c r="J23" s="6" t="inlineStr">
@@ -1735,12 +1815,16 @@
           <t>休</t>
         </is>
       </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>③</t>
-        </is>
-      </c>
-      <c r="L23" s="5" t="n"/>
+      <c r="K23" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>②</t>
+        </is>
+      </c>
       <c r="M23" s="5" t="n"/>
     </row>
     <row r="24">
@@ -1755,9 +1839,9 @@
       <c r="C24" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>①</t>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -1770,9 +1854,9 @@
           <t>休</t>
         </is>
       </c>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>④</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
@@ -1780,9 +1864,9 @@
           <t>休</t>
         </is>
       </c>
-      <c r="I24" s="5" t="inlineStr">
-        <is>
-          <t>①</t>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
@@ -1790,12 +1874,16 @@
           <t>②</t>
         </is>
       </c>
-      <c r="K24" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="L24" s="5" t="n"/>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>④</t>
+        </is>
+      </c>
+      <c r="L24" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
       <c r="M24" s="5" t="n"/>
     </row>
     <row r="25">
@@ -1810,14 +1898,14 @@
       <c r="C25" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>①</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>②</t>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
@@ -1825,32 +1913,36 @@
           <t>休</t>
         </is>
       </c>
-      <c r="G25" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="H25" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>②</t>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>④</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>①</t>
-        </is>
-      </c>
-      <c r="K25" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="L25" s="5" t="n"/>
+          <t>④</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="L25" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
       <c r="M25" s="5" t="n"/>
     </row>
     <row r="26">
@@ -1870,9 +1962,9 @@
           <t>①</t>
         </is>
       </c>
-      <c r="E26" s="8" t="inlineStr">
-        <is>
-          <t>②</t>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr">
@@ -1887,25 +1979,29 @@
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="I26" s="8" t="inlineStr">
+        <is>
+          <t>③</t>
+        </is>
+      </c>
+      <c r="J26" s="8" t="inlineStr">
+        <is>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="K26" s="8" t="inlineStr">
+        <is>
           <t>①</t>
         </is>
       </c>
-      <c r="I26" s="8" t="inlineStr">
+      <c r="L26" s="8" t="inlineStr">
         <is>
           <t>④</t>
         </is>
       </c>
-      <c r="J26" s="8" t="inlineStr">
-        <is>
-          <t>③</t>
-        </is>
-      </c>
-      <c r="K26" s="8" t="inlineStr">
-        <is>
-          <t>②</t>
-        </is>
-      </c>
-      <c r="L26" s="5" t="n"/>
       <c r="M26" s="5" t="n"/>
     </row>
     <row r="27">
@@ -1935,32 +2031,36 @@
           <t>③</t>
         </is>
       </c>
-      <c r="G27" s="10" t="inlineStr">
-        <is>
-          <t>④</t>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="I27" s="10" t="inlineStr">
+        <is>
+          <t>③</t>
+        </is>
+      </c>
+      <c r="J27" s="10" t="inlineStr">
+        <is>
           <t>②</t>
         </is>
       </c>
-      <c r="I27" s="10" t="inlineStr">
-        <is>
-          <t>④</t>
-        </is>
-      </c>
-      <c r="J27" s="10" t="inlineStr">
-        <is>
-          <t>③</t>
-        </is>
-      </c>
       <c r="K27" s="10" t="inlineStr">
         <is>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="L27" s="10" t="inlineStr">
+        <is>
           <t>①</t>
         </is>
       </c>
-      <c r="L27" s="5" t="n"/>
       <c r="M27" s="5" t="n"/>
     </row>
     <row r="28">
@@ -1975,9 +2075,9 @@
       <c r="C28" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>①</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -1990,32 +2090,36 @@
           <t>③</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
-        <is>
-          <t>④</t>
-        </is>
-      </c>
-      <c r="H28" s="5" t="inlineStr">
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>①</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="K28" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="L28" s="5" t="inlineStr">
         <is>
           <t>③</t>
         </is>
       </c>
-      <c r="I28" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="J28" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="K28" s="5" t="inlineStr">
-        <is>
-          <t>④</t>
-        </is>
-      </c>
-      <c r="L28" s="5" t="n"/>
       <c r="M28" s="5" t="n"/>
     </row>
     <row r="29">
@@ -2035,14 +2139,14 @@
           <t>休</t>
         </is>
       </c>
-      <c r="E29" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>③</t>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>②</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
@@ -2050,14 +2154,14 @@
           <t>④</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>③</t>
-        </is>
-      </c>
-      <c r="I29" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>④</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr">
@@ -2065,12 +2169,16 @@
           <t>休</t>
         </is>
       </c>
-      <c r="K29" s="5" t="inlineStr">
-        <is>
-          <t>④</t>
-        </is>
-      </c>
-      <c r="L29" s="5" t="n"/>
+      <c r="K29" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>②</t>
+        </is>
+      </c>
       <c r="M29" s="5" t="n"/>
     </row>
     <row r="30">
@@ -2085,9 +2193,9 @@
       <c r="C30" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>①</t>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -2100,9 +2208,9 @@
           <t>休</t>
         </is>
       </c>
-      <c r="G30" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>④</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
@@ -2110,22 +2218,26 @@
           <t>休</t>
         </is>
       </c>
-      <c r="I30" s="5" t="inlineStr">
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>④</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="inlineStr">
         <is>
           <t>②</t>
         </is>
       </c>
-      <c r="J30" s="5" t="inlineStr">
-        <is>
-          <t>①</t>
-        </is>
-      </c>
-      <c r="K30" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="L30" s="5" t="n"/>
+      <c r="L30" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
       <c r="M30" s="5" t="n"/>
     </row>
     <row r="31">
@@ -2145,9 +2257,9 @@
           <t>①</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>②</t>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
@@ -2160,27 +2272,31 @@
           <t>休</t>
         </is>
       </c>
-      <c r="H31" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="I31" s="5" t="inlineStr">
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="J31" s="5" t="inlineStr">
-        <is>
-          <t>②</t>
-        </is>
-      </c>
-      <c r="K31" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="L31" s="5" t="n"/>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="L31" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
       <c r="M31" s="5" t="n"/>
     </row>
     <row r="32">
@@ -2210,19 +2326,19 @@
           <t>③</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr">
-        <is>
-          <t>④</t>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>④</t>
-        </is>
-      </c>
-      <c r="I32" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>③</t>
         </is>
       </c>
       <c r="J32" s="6" t="inlineStr">
@@ -2230,12 +2346,16 @@
           <t>休</t>
         </is>
       </c>
-      <c r="K32" s="5" t="inlineStr">
-        <is>
-          <t>③</t>
-        </is>
-      </c>
-      <c r="L32" s="5" t="n"/>
+      <c r="K32" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>⑤</t>
+        </is>
+      </c>
       <c r="M32" s="5" t="n"/>
     </row>
     <row r="33">
@@ -2250,9 +2370,9 @@
       <c r="C33" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>①</t>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
@@ -2272,25 +2392,29 @@
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>①</t>
+          <t>⑤</t>
         </is>
       </c>
       <c r="I33" s="8" t="inlineStr">
         <is>
+          <t>②</t>
+        </is>
+      </c>
+      <c r="J33" s="8" t="inlineStr">
+        <is>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="K33" s="8" t="inlineStr">
+        <is>
           <t>③</t>
         </is>
       </c>
-      <c r="J33" s="8" t="inlineStr">
+      <c r="L33" s="8" t="inlineStr">
         <is>
           <t>④</t>
         </is>
       </c>
-      <c r="K33" s="8" t="inlineStr">
-        <is>
-          <t>②</t>
-        </is>
-      </c>
-      <c r="L33" s="5" t="n"/>
       <c r="M33" s="5" t="n"/>
     </row>
     <row r="34">
@@ -2304,19 +2428,19 @@
         <v>80</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H34" s="5" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I34" s="5" t="n">
         <v>20</v>
@@ -2327,7 +2451,9 @@
       <c r="K34" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="L34" s="5" t="n"/>
+      <c r="L34" s="5" t="n">
+        <v>20</v>
+      </c>
       <c r="M34" s="5" t="n"/>
     </row>
     <row r="35">
@@ -2425,12 +2551,12 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>船木智一 ／ 新田</t>
+          <t>船木智一 ／ 古川</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>和田陽向太 ／ 古川</t>
+          <t>和田陽向太 ／ 山口</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr"/>
@@ -2450,18 +2576,18 @@
       <c r="C3" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D3" s="5" t="inlineStr"/>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>船木智一 ／ 新田</t>
+        </is>
+      </c>
       <c r="E3" s="5" t="inlineStr"/>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>永井海里 ／ 山谷大地</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>横山凌 ／ 山口</t>
-        </is>
-      </c>
+          <t>永井海里 ／ 徳留</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
@@ -2479,14 +2605,10 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>船木智一 ／ 山谷大地</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>和田陽向太 ／ 山口</t>
-        </is>
-      </c>
+          <t>船木智一 ／ 徳留</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr"/>
       <c r="F4" s="5" t="inlineStr">
         <is>
           <t>永井海里 ／ 古川</t>
@@ -2494,7 +2616,7 @@
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>横山凌 ／ 新田</t>
+          <t>山谷大地 ／ 山口</t>
         </is>
       </c>
     </row>
@@ -2512,14 +2634,10 @@
       <c r="C5" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>船木智一 ／ 古川</t>
-        </is>
-      </c>
+      <c r="D5" s="5" t="inlineStr"/>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>和田陽向太 ／ 新田</t>
+          <t>和田陽向太 ／ 古川</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -2529,7 +2647,7 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>横山凌 ／ 山谷大地</t>
+          <t>山谷大地 ／ 新田</t>
         </is>
       </c>
     </row>
@@ -2548,15 +2666,15 @@
         <v>2</v>
       </c>
       <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>永井海里 ／ 山谷大地</t>
-        </is>
-      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>和田陽向太 ／ 新田</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr"/>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>横山凌 ／ 山口</t>
+          <t>山谷大地 ／ 徳留</t>
         </is>
       </c>
     </row>
@@ -2576,16 +2694,16 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>船木智一 ／ 新田</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>和田陽向太 ／ 古川</t>
-        </is>
-      </c>
+          <t>船木智一 ／ 山口</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr"/>
       <c r="F7" s="5" t="inlineStr"/>
-      <c r="G7" s="5" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>山谷大地 ／ 古川</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
@@ -2603,15 +2721,15 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>船木智一 ／ 古川</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>和田陽向太 ／ 新田</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr"/>
+          <t>船木智一 ／ 山口</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>永井海里 ／ 古川</t>
+        </is>
+      </c>
       <c r="G8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
@@ -2629,17 +2747,13 @@
         <v>2</v>
       </c>
       <c r="D9" s="5" t="inlineStr"/>
-      <c r="E9" s="5" t="inlineStr"/>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>永井海里 ／ 山口</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>横山凌 ／ 山谷大地</t>
-        </is>
-      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>和田陽向太 ／ 徳留</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
@@ -2656,17 +2770,13 @@
         <v>2</v>
       </c>
       <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>永井海里 ／ 山谷大地</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>横山凌 ／ 山口</t>
-        </is>
-      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>和田陽向太 ／ 新田</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
@@ -2684,12 +2794,12 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>船木智一 ／ 山口</t>
+          <t>船木智一 ／ 古川</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>和田陽向太 ／ 山谷大地</t>
+          <t>和田陽向太 ／ 徳留</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -2699,7 +2809,7 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>横山凌 ／ 古川</t>
+          <t>山谷大地 ／ 山口</t>
         </is>
       </c>
     </row>
@@ -2719,7 +2829,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>船木智一 ／ 山谷大地</t>
+          <t>船木智一 ／ 徳留</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -2729,14 +2839,10 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>永井海里 ／ 古川</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>横山凌 ／ 新田</t>
-        </is>
-      </c>
+          <t>永井海里 ／ 新田</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
@@ -2752,18 +2858,18 @@
       <c r="C13" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>船木智一 ／ 新田</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>和田陽向太 ／ 古川</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr"/>
-      <c r="G13" s="5" t="inlineStr"/>
+      <c r="D13" s="5" t="inlineStr"/>
+      <c r="E13" s="5" t="inlineStr"/>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>永井海里 ／ 山口</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>山谷大地 ／ 古川</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
@@ -2781,16 +2887,16 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>船木智一 ／ 古川</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>和田陽向太 ／ 新田</t>
-        </is>
-      </c>
+          <t>船木智一 ／ 山口</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr"/>
       <c r="F14" s="5" t="inlineStr"/>
-      <c r="G14" s="5" t="inlineStr"/>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>山谷大地 ／ 古川</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
@@ -2808,14 +2914,10 @@
       </c>
       <c r="D15" s="5" t="inlineStr"/>
       <c r="E15" s="5" t="inlineStr"/>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>永井海里 ／ 山口</t>
-        </is>
-      </c>
+      <c r="F15" s="5" t="inlineStr"/>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>横山凌 ／ 山谷大地</t>
+          <t>山谷大地 ／ 新田</t>
         </is>
       </c>
     </row>
@@ -2837,14 +2939,10 @@
       <c r="E16" s="5" t="inlineStr"/>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>永井海里 ／ 山口</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>横山凌 ／ 山谷大地</t>
-        </is>
-      </c>
+          <t>永井海里 ／ 徳留</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
@@ -2862,12 +2960,12 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>船木智一 ／ 新田</t>
+          <t>船木智一 ／ 古川</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>和田陽向太 ／ 古川</t>
+          <t>和田陽向太 ／ 山口</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr"/>
@@ -2889,22 +2987,18 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>船木智一 ／ 山口</t>
+          <t>船木智一 ／ 新田</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>和田陽向太 ／ 山谷大地</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>永井海里 ／ 新田</t>
-        </is>
-      </c>
+          <t>和田陽向太 ／ 古川</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr"/>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>横山凌 ／ 古川</t>
+          <t>山谷大地 ／ 徳留</t>
         </is>
       </c>
     </row>
@@ -2924,22 +3018,22 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>船木智一 ／ 山口</t>
+          <t>船木智一 ／ 徳留</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>和田陽向太 ／ 山谷大地</t>
+          <t>和田陽向太 ／ 新田</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>永井海里 ／ 新田</t>
+          <t>永井海里 ／ 古川</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>横山凌 ／ 古川</t>
+          <t>山谷大地 ／ 山口</t>
         </is>
       </c>
     </row>
@@ -2957,17 +3051,13 @@
       <c r="C20" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>船木智一 ／ 古川</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>和田陽向太 ／ 新田</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="inlineStr"/>
+      <c r="D20" s="5" t="inlineStr"/>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>永井海里 ／ 山口</t>
+        </is>
+      </c>
       <c r="G20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
@@ -2988,14 +3078,10 @@
       <c r="E21" s="5" t="inlineStr"/>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>永井海里 ／ 山谷大地</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>横山凌 ／ 山口</t>
-        </is>
-      </c>
+          <t>永井海里 ／ 徳留</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
@@ -3011,18 +3097,18 @@
       <c r="C22" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>永井海里 ／ 山口</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>横山凌 ／ 山谷大地</t>
-        </is>
-      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>船木智一 ／ 新田</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>和田陽向太 ／ 徳留</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
@@ -3038,18 +3124,18 @@
       <c r="C23" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>船木智一 ／ 新田</t>
-        </is>
-      </c>
+      <c r="D23" s="5" t="inlineStr"/>
       <c r="E23" s="5" t="inlineStr">
         <is>
           <t>和田陽向太 ／ 古川</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>山谷大地 ／ 山口</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
@@ -3065,18 +3151,14 @@
       <c r="C24" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>船木智一 ／ 古川</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>和田陽向太 ／ 新田</t>
-        </is>
-      </c>
+      <c r="D24" s="5" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr"/>
       <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>山谷大地 ／ 古川</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
@@ -3094,22 +3176,18 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>船木智一 ／ 山谷大地</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>和田陽向太 ／ 山口</t>
-        </is>
-      </c>
+          <t>船木智一 ／ 山口</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr"/>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>永井海里 ／ 古川</t>
+          <t>永井海里 ／ 新田</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>横山凌 ／ 新田</t>
+          <t>山谷大地 ／ 徳留</t>
         </is>
       </c>
     </row>
@@ -3129,24 +3207,20 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>船木智一 ／ 山口</t>
+          <t>船木智一 ／ 徳留</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>和田陽向太 ／ 山谷大地</t>
+          <t>和田陽向太 ／ 古川</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>永井海里 ／ 古川</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr">
-        <is>
-          <t>横山凌 ／ 新田</t>
-        </is>
-      </c>
+          <t>永井海里 ／ 新田</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
@@ -3162,18 +3236,18 @@
       <c r="C27" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D27" s="5" t="inlineStr"/>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>船木智一 ／ 新田</t>
+        </is>
+      </c>
       <c r="E27" s="5" t="inlineStr"/>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>永井海里 ／ 山谷大地</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr">
-        <is>
-          <t>横山凌 ／ 山口</t>
-        </is>
-      </c>
+          <t>永井海里 ／ 徳留</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
@@ -3190,15 +3264,15 @@
         <v>2</v>
       </c>
       <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>永井海里 ／ 山谷大地</t>
-        </is>
-      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>和田陽向太 ／ 徳留</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr"/>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>横山凌 ／ 山口</t>
+          <t>山谷大地 ／ 新田</t>
         </is>
       </c>
     </row>
@@ -3216,18 +3290,18 @@
       <c r="C29" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>船木智一 ／ 古川</t>
-        </is>
-      </c>
+      <c r="D29" s="5" t="inlineStr"/>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>和田陽向太 ／ 新田</t>
+          <t>和田陽向太 ／ 山口</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>山谷大地 ／ 古川</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
@@ -3245,14 +3319,10 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>船木智一 ／ 新田</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>和田陽向太 ／ 古川</t>
-        </is>
-      </c>
+          <t>船木智一 ／ 古川</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr"/>
       <c r="F30" s="5" t="inlineStr"/>
       <c r="G30" s="5" t="inlineStr"/>
     </row>
@@ -3274,14 +3344,10 @@
       <c r="E31" s="5" t="inlineStr"/>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>永井海里 ／ 山口</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr">
-        <is>
-          <t>横山凌 ／ 山谷大地</t>
-        </is>
-      </c>
+          <t>永井海里 ／ 新田</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
@@ -3297,24 +3363,20 @@
       <c r="C32" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>船木智一 ／ 山谷大地</t>
-        </is>
-      </c>
+      <c r="D32" s="5" t="inlineStr"/>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>和田陽向太 ／ 山口</t>
+          <t>和田陽向太 ／ 新田</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>永井海里 ／ 新田</t>
+          <t>永井海里 ／ 山口</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>横山凌 ／ 古川</t>
+          <t>山谷大地 ／ 徳留</t>
         </is>
       </c>
     </row>
@@ -3329,7 +3391,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -3395,7 +3457,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>①船木智一、②和田陽向太、③永井海里、④横山凌</t>
+          <t>①船木智一、②和田陽向太、③永井海里、④山谷大地、⑤横山凌</t>
         </is>
       </c>
     </row>
@@ -3407,7 +3469,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>山谷大地、新田、古川、山口</t>
+          <t>新田、古川、山口、徳留</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3495,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>出勤20日／土日9日／公休11日／最大4連勤</t>
+          <t>出勤16日／土日7日／公休15日／最大3連勤</t>
         </is>
       </c>
     </row>
@@ -3445,7 +3507,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>出勤20日／土日9日／公休11日／最大4連勤</t>
+          <t>出勤16日／土日7日／公休15日／最大4連勤</t>
         </is>
       </c>
     </row>
@@ -3457,31 +3519,31 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>出勤20日／土日9日／公休11日／最大4連勤</t>
+          <t>出勤16日／土日8日／公休15日／最大3連勤</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>横山凌</t>
+          <t>山谷大地</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>出勤20日／土日9日／公休11日／最大4連勤</t>
+          <t>出勤16日／土日7日／公休15日／最大4連勤</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>山谷大地</t>
+          <t>横山凌</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>出勤20日／土日9日／公休11日／最大4連勤</t>
+          <t>出勤16日／土日7日／公休15日／最大3連勤</t>
         </is>
       </c>
     </row>
@@ -3516,6 +3578,18 @@
         </is>
       </c>
       <c r="B19" t="inlineStr">
+        <is>
+          <t>出勤20日／土日9日／公休11日／最大4連勤</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>徳留</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
         <is>
           <t>出勤20日／土日9日／公休11日／最大4連勤</t>
         </is>

--- a/2026年10月_出勤表.xlsx
+++ b/2026年10月_出勤表.xlsx
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
@@ -610,39 +610,39 @@
           <t>②</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="G3" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="H3" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="I3" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="J3" s="5" t="inlineStr">
-        <is>
-          <t>①</t>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>③</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>②</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>②</t>
-        </is>
-      </c>
-      <c r="L3" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+          <t>①</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>③</t>
         </is>
       </c>
       <c r="M3" s="5" t="n"/>
@@ -657,21 +657,21 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>③</t>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>②</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -679,29 +679,29 @@
           <t>休</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="I4" s="5" t="inlineStr">
-        <is>
-          <t>①</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="K4" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>①</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>②</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>③</t>
+          <t>⑤</t>
         </is>
       </c>
       <c r="M4" s="5" t="n"/>
@@ -718,14 +718,14 @@
       <c r="C5" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>①</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>②</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
@@ -745,22 +745,22 @@
       </c>
       <c r="I5" s="8" t="inlineStr">
         <is>
-          <t>⑤</t>
+          <t>③</t>
         </is>
       </c>
       <c r="J5" s="8" t="inlineStr">
         <is>
-          <t>③</t>
+          <t>④</t>
         </is>
       </c>
       <c r="K5" s="8" t="inlineStr">
         <is>
-          <t>④</t>
+          <t>⑤</t>
         </is>
       </c>
       <c r="L5" s="8" t="inlineStr">
         <is>
-          <t>①</t>
+          <t>②</t>
         </is>
       </c>
       <c r="M5" s="5" t="n"/>
@@ -777,9 +777,9 @@
       <c r="C6" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>①</t>
         </is>
       </c>
       <c r="E6" s="10" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>⑤</t>
+          <t>①</t>
         </is>
       </c>
       <c r="I6" s="10" t="inlineStr">
@@ -817,9 +817,9 @@
           <t>③</t>
         </is>
       </c>
-      <c r="L6" s="10" t="inlineStr">
-        <is>
-          <t>⑤</t>
+      <c r="L6" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="M6" s="5" t="n"/>
@@ -834,16 +834,16 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>②</t>
+        <v>3</v>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>①</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
@@ -856,19 +856,19 @@
           <t>④</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>⑤</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>②</t>
-        </is>
-      </c>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+          <t>①</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>⑤</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
@@ -905,9 +905,9 @@
           <t>休</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>③</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -920,24 +920,24 @@
           <t>休</t>
         </is>
       </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>④</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>④</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>①</t>
-        </is>
-      </c>
-      <c r="L8" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+          <t>③</t>
+        </is>
+      </c>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>①</t>
         </is>
       </c>
       <c r="M8" s="5" t="n"/>
@@ -952,46 +952,46 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>②</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>③</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+          <t>①</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>④</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>⑤</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>③</t>
+          <t>②</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>①</t>
+          <t>④</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr">
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
@@ -1020,17 +1020,17 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>②</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>③</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>④</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
@@ -1038,9 +1038,9 @@
           <t>⑤</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>⑤</t>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
@@ -1048,14 +1048,14 @@
           <t>休</t>
         </is>
       </c>
-      <c r="K10" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>③</t>
         </is>
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>②</t>
+          <t>④</t>
         </is>
       </c>
       <c r="M10" s="5" t="n"/>
@@ -1070,11 +1070,11 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+        <v>3</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>①</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1107,9 +1107,9 @@
           <t>休</t>
         </is>
       </c>
-      <c r="K11" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>①</t>
         </is>
       </c>
       <c r="L11" s="5" t="inlineStr">
@@ -1146,19 +1146,19 @@
           <t>③</t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
-          <t>④</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>⑤</t>
         </is>
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>③</t>
+          <t>⑤</t>
         </is>
       </c>
       <c r="J12" s="8" t="inlineStr">
@@ -1168,12 +1168,12 @@
       </c>
       <c r="K12" s="8" t="inlineStr">
         <is>
-          <t>④</t>
+          <t>②</t>
         </is>
       </c>
       <c r="L12" s="8" t="inlineStr">
         <is>
-          <t>②</t>
+          <t>③</t>
         </is>
       </c>
       <c r="M12" s="5" t="n"/>
@@ -1200,14 +1200,14 @@
           <t>②</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr">
-        <is>
-          <t>③</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>④</t>
         </is>
       </c>
       <c r="H13" s="10" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="I13" s="10" t="inlineStr">
         <is>
-          <t>③</t>
+          <t>①</t>
         </is>
       </c>
       <c r="J13" s="10" t="inlineStr">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="K13" s="10" t="inlineStr">
         <is>
-          <t>②</t>
+          <t>④</t>
         </is>
       </c>
       <c r="L13" s="10" t="inlineStr">
         <is>
-          <t>①</t>
+          <t>②</t>
         </is>
       </c>
       <c r="M13" s="5" t="n"/>
@@ -1247,16 +1247,16 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
           <t>休</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>②</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -1269,14 +1269,14 @@
           <t>④</t>
         </is>
       </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>③</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>③</t>
-        </is>
-      </c>
-      <c r="L14" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>②</t>
         </is>
       </c>
       <c r="M14" s="5" t="n"/>
@@ -1306,7 +1306,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
@@ -1318,9 +1318,9 @@
           <t>休</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>③</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
@@ -1333,24 +1333,24 @@
           <t>休</t>
         </is>
       </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>④</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>④</t>
-        </is>
-      </c>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
-          <t>①</t>
-        </is>
-      </c>
-      <c r="L15" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+          <t>③</t>
+        </is>
+      </c>
+      <c r="K15" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>①</t>
         </is>
       </c>
       <c r="M15" s="5" t="n"/>
@@ -1365,51 +1365,51 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>④</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>⑤</t>
+        <v>3</v>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>①</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>②</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>③</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>④</t>
-        </is>
-      </c>
-      <c r="J16" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="K16" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="L16" s="5" t="inlineStr">
-        <is>
-          <t>⑤</t>
+          <t>①</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>③</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>②</t>
+        </is>
+      </c>
+      <c r="L16" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="M16" s="5" t="n"/>
@@ -1424,16 +1424,16 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+        <v>3</v>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>②</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>②</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -1441,9 +1441,9 @@
           <t>③</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>③</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
@@ -1451,14 +1451,14 @@
           <t>⑤</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>⑤</t>
-        </is>
-      </c>
-      <c r="J17" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>⑤</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
@@ -1466,9 +1466,9 @@
           <t>休</t>
         </is>
       </c>
-      <c r="L17" s="5" t="inlineStr">
-        <is>
-          <t>③</t>
+      <c r="L17" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="M17" s="5" t="n"/>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
@@ -1495,39 +1495,39 @@
           <t>②</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="J18" s="5" t="inlineStr">
-        <is>
-          <t>①</t>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>③</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>④</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>③</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>②</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>②</t>
-        </is>
-      </c>
-      <c r="L18" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+          <t>①</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>④</t>
         </is>
       </c>
       <c r="M18" s="5" t="n"/>
@@ -1554,14 +1554,14 @@
           <t>②</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="G19" s="8" t="inlineStr">
-        <is>
-          <t>④</t>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>③</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="I19" s="8" t="inlineStr">
         <is>
-          <t>①</t>
+          <t>③</t>
         </is>
       </c>
       <c r="J19" s="8" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="L19" s="8" t="inlineStr">
         <is>
-          <t>④</t>
+          <t>①</t>
         </is>
       </c>
       <c r="M19" s="5" t="n"/>
@@ -1613,9 +1613,9 @@
           <t>②</t>
         </is>
       </c>
-      <c r="F20" s="10" t="inlineStr">
-        <is>
-          <t>③</t>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="G20" s="10" t="inlineStr">
@@ -1623,9 +1623,9 @@
           <t>④</t>
         </is>
       </c>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+      <c r="H20" s="10" t="inlineStr">
+        <is>
+          <t>⑤</t>
         </is>
       </c>
       <c r="I20" s="10" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="J20" s="10" t="inlineStr">
         <is>
-          <t>③</t>
+          <t>①</t>
         </is>
       </c>
       <c r="K20" s="10" t="inlineStr">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="L20" s="10" t="inlineStr">
         <is>
-          <t>①</t>
+          <t>⑤</t>
         </is>
       </c>
       <c r="M20" s="5" t="n"/>
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
@@ -1677,9 +1677,9 @@
           <t>③</t>
         </is>
       </c>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>④</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
@@ -1687,24 +1687,24 @@
           <t>⑤</t>
         </is>
       </c>
-      <c r="I21" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="J21" s="5" t="inlineStr">
-        <is>
-          <t>⑤</t>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>③</t>
-        </is>
-      </c>
-      <c r="L21" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+          <t>④</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>③</t>
         </is>
       </c>
       <c r="M21" s="5" t="n"/>
@@ -1719,7 +1719,7 @@
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
@@ -1736,9 +1736,9 @@
           <t>③</t>
         </is>
       </c>
-      <c r="G22" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>④</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>⑤</t>
-        </is>
-      </c>
-      <c r="J22" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+          <t>③</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>④</t>
         </is>
       </c>
       <c r="K22" s="6" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>③</t>
+          <t>⑤</t>
         </is>
       </c>
       <c r="M22" s="5" t="n"/>
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
@@ -1795,9 +1795,9 @@
           <t>休</t>
         </is>
       </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>④</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
@@ -1807,22 +1807,22 @@
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>①</t>
-        </is>
-      </c>
-      <c r="J23" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="K23" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="L23" s="5" t="inlineStr">
-        <is>
-          <t>②</t>
+          <t>④</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>②</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>①</t>
+        </is>
+      </c>
+      <c r="L23" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="M23" s="5" t="n"/>
@@ -1837,11 +1837,11 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+        <v>4</v>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>④</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -1849,9 +1849,9 @@
           <t>②</t>
         </is>
       </c>
-      <c r="F24" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>③</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
@@ -1859,9 +1859,9 @@
           <t>④</t>
         </is>
       </c>
-      <c r="H24" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>⑤</t>
         </is>
       </c>
       <c r="I24" s="6" t="inlineStr">
@@ -1871,17 +1871,17 @@
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>②</t>
+          <t>⑤</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>④</t>
-        </is>
-      </c>
-      <c r="L24" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+          <t>③</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>②</t>
         </is>
       </c>
       <c r="M24" s="5" t="n"/>
@@ -1896,31 +1896,31 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>④</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>⑤</t>
+        <v>3</v>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>①</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>②</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>③</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
@@ -1930,17 +1930,17 @@
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>④</t>
+          <t>③</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>⑤</t>
-        </is>
-      </c>
-      <c r="L25" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+          <t>②</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>①</t>
         </is>
       </c>
       <c r="M25" s="5" t="n"/>
@@ -1962,9 +1962,9 @@
           <t>①</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>③</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr">
@@ -1984,17 +1984,17 @@
       </c>
       <c r="I26" s="8" t="inlineStr">
         <is>
-          <t>③</t>
+          <t>⑤</t>
         </is>
       </c>
       <c r="J26" s="8" t="inlineStr">
         <is>
-          <t>⑤</t>
-        </is>
-      </c>
-      <c r="K26" s="8" t="inlineStr">
-        <is>
-          <t>①</t>
+          <t>①</t>
+        </is>
+      </c>
+      <c r="K26" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="L26" s="8" t="inlineStr">
@@ -2021,9 +2021,9 @@
           <t>①</t>
         </is>
       </c>
-      <c r="E27" s="10" t="inlineStr">
-        <is>
-          <t>②</t>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="F27" s="10" t="inlineStr">
@@ -2031,9 +2031,9 @@
           <t>③</t>
         </is>
       </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+      <c r="G27" s="10" t="inlineStr">
+        <is>
+          <t>④</t>
         </is>
       </c>
       <c r="H27" s="10" t="inlineStr">
@@ -2043,12 +2043,12 @@
       </c>
       <c r="I27" s="10" t="inlineStr">
         <is>
-          <t>③</t>
+          <t>①</t>
         </is>
       </c>
       <c r="J27" s="10" t="inlineStr">
         <is>
-          <t>②</t>
+          <t>④</t>
         </is>
       </c>
       <c r="K27" s="10" t="inlineStr">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="L27" s="10" t="inlineStr">
         <is>
-          <t>①</t>
+          <t>③</t>
         </is>
       </c>
       <c r="M27" s="5" t="n"/>
@@ -2073,21 +2073,21 @@
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>②</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>③</t>
+          <t>⑤</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
@@ -2095,9 +2095,9 @@
           <t>休</t>
         </is>
       </c>
-      <c r="H28" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>⑤</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
@@ -2110,14 +2110,14 @@
           <t>休</t>
         </is>
       </c>
-      <c r="K28" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="L28" s="5" t="inlineStr">
-        <is>
-          <t>③</t>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>②</t>
+        </is>
+      </c>
+      <c r="L28" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="M28" s="5" t="n"/>
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
@@ -2144,9 +2144,9 @@
           <t>②</t>
         </is>
       </c>
-      <c r="F29" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>③</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
@@ -2154,24 +2154,24 @@
           <t>④</t>
         </is>
       </c>
-      <c r="H29" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>⑤</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>④</t>
-        </is>
-      </c>
-      <c r="J29" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="K29" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>④</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>③</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
@@ -2213,29 +2213,29 @@
           <t>④</t>
         </is>
       </c>
-      <c r="H30" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="I30" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>②</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>④</t>
-        </is>
-      </c>
-      <c r="K30" s="5" t="inlineStr">
-        <is>
-          <t>②</t>
-        </is>
-      </c>
-      <c r="L30" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="K30" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>④</t>
         </is>
       </c>
       <c r="M30" s="5" t="n"/>
@@ -2250,16 +2250,16 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="E31" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>②</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
@@ -2277,14 +2277,14 @@
           <t>⑤</t>
         </is>
       </c>
-      <c r="I31" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>①</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>①</t>
+          <t>②</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
@@ -2309,11 +2309,11 @@
         </is>
       </c>
       <c r="C32" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+        <v>3</v>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>①</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
@@ -2326,34 +2326,34 @@
           <t>③</t>
         </is>
       </c>
-      <c r="G32" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>⑤</t>
-        </is>
-      </c>
-      <c r="I32" s="5" t="inlineStr">
-        <is>
-          <t>③</t>
-        </is>
-      </c>
-      <c r="J32" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="K32" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>④</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>①</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="inlineStr">
+        <is>
+          <t>④</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>⑤</t>
+          <t>③</t>
         </is>
       </c>
       <c r="M32" s="5" t="n"/>
@@ -2370,9 +2370,9 @@
       <c r="C33" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>休</t>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>①</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
@@ -2392,27 +2392,27 @@
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>⑤</t>
+          <t>②</t>
         </is>
       </c>
       <c r="I33" s="8" t="inlineStr">
         <is>
-          <t>②</t>
+          <t>④</t>
         </is>
       </c>
       <c r="J33" s="8" t="inlineStr">
         <is>
-          <t>⑤</t>
-        </is>
-      </c>
-      <c r="K33" s="8" t="inlineStr">
-        <is>
-          <t>③</t>
+          <t>③</t>
+        </is>
+      </c>
+      <c r="K33" s="6" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="L33" s="8" t="inlineStr">
         <is>
-          <t>④</t>
+          <t>①</t>
         </is>
       </c>
       <c r="M33" s="5" t="n"/>
@@ -2425,34 +2425,34 @@
       </c>
       <c r="B34" s="5" t="n"/>
       <c r="C34" s="5" t="n">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="H34" s="5" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="M34" s="5" t="n"/>
     </row>
@@ -2486,16 +2486,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="5" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2516,22 +2517,27 @@
       </c>
       <c r="D1" s="11" t="inlineStr">
         <is>
-          <t>①号車</t>
+          <t>①船木智一</t>
         </is>
       </c>
       <c r="E1" s="11" t="inlineStr">
         <is>
-          <t>②号車</t>
+          <t>②和田陽向太</t>
         </is>
       </c>
       <c r="F1" s="11" t="inlineStr">
         <is>
-          <t>③号車</t>
+          <t>③永井海里</t>
         </is>
       </c>
       <c r="G1" s="11" t="inlineStr">
         <is>
-          <t>④号車</t>
+          <t>④山谷大地</t>
+        </is>
+      </c>
+      <c r="H1" s="11" t="inlineStr">
+        <is>
+          <t>⑤横山凌</t>
         </is>
       </c>
     </row>
@@ -2547,20 +2553,33 @@
         </is>
       </c>
       <c r="C2" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>船木智一 ／ 古川</t>
+          <t>山口</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>和田陽向太 ／ 山口</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="inlineStr"/>
-      <c r="G2" s="5" t="inlineStr"/>
+          <t>新田</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>徳留</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>運休</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>山谷大地</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
@@ -2574,20 +2593,33 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>船木智一 ／ 新田</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr"/>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>永井海里 ／ 徳留</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr"/>
+          <t>古川</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>山口</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>運休</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>運休</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>徳留</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
@@ -2603,20 +2635,29 @@
       <c r="C4" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>船木智一 ／ 徳留</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr"/>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>運休</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>徳留</t>
+        </is>
+      </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>永井海里 ／ 古川</t>
+          <t>新田</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>山谷大地 ／ 山口</t>
+          <t>古川</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>山口</t>
         </is>
       </c>
     </row>
@@ -2634,20 +2675,29 @@
       <c r="C5" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="D5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>横山凌</t>
+        </is>
+      </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>和田陽向太 ／ 古川</t>
+          <t>古川</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>永井海里 ／ 山口</t>
+          <t>山口</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>山谷大地 ／ 新田</t>
+          <t>新田</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>運休</t>
         </is>
       </c>
     </row>
@@ -2663,18 +2713,31 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>和田陽向太 ／ 新田</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>新田</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>運休</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>運休</t>
+        </is>
+      </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>山谷大地 ／ 徳留</t>
+          <t>徳留</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>古川</t>
         </is>
       </c>
     </row>
@@ -2690,18 +2753,31 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>船木智一 ／ 山口</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr"/>
-      <c r="F7" s="5" t="inlineStr"/>
+          <t>徳留</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>運休</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>古川</t>
+        </is>
+      </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>山谷大地 ／ 古川</t>
+          <t>新田</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>運休</t>
         </is>
       </c>
     </row>
@@ -2717,20 +2793,33 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>船木智一 ／ 山口</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr"/>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>永井海里 ／ 古川</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr"/>
+          <t>永井海里</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>古川</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>運休</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>山口</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>新田</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
@@ -2744,16 +2833,33 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D9" s="5" t="inlineStr"/>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>和田陽向太 ／ 徳留</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr"/>
-      <c r="G9" s="5" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>運休</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>運休</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>山口</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>徳留</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>和田陽向太</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
@@ -2767,16 +2873,33 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D10" s="5" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>山口</t>
+        </is>
+      </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>和田陽向太 ／ 新田</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
+          <t>新田</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>運休</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>運休</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>徳留</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
@@ -2794,22 +2917,27 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>船木智一 ／ 古川</t>
+          <t>古川</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>和田陽向太 ／ 徳留</t>
+          <t>山口</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>永井海里 ／ 新田</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>山谷大地 ／ 山口</t>
+          <t>徳留</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>運休</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>新田</t>
         </is>
       </c>
     </row>
@@ -2829,20 +2957,29 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>船木智一 ／ 徳留</t>
+          <t>新田</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>和田陽向太 ／ 山口</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>永井海里 ／ 新田</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr"/>
+          <t>徳留</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>運休</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>山口</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>古川</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
@@ -2856,18 +2993,31 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D13" s="5" t="inlineStr"/>
-      <c r="E13" s="5" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>運休</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>徳留</t>
+        </is>
+      </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>永井海里 ／ 山口</t>
+          <t>新田</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>山谷大地 ／ 古川</t>
+          <t>古川</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>山口</t>
         </is>
       </c>
     </row>
@@ -2883,18 +3033,31 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>船木智一 ／ 山口</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr"/>
-      <c r="F14" s="5" t="inlineStr"/>
+          <t>徳留</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>運休</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>古川</t>
+        </is>
+      </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>山谷大地 ／ 古川</t>
+          <t>新田</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>運休</t>
         </is>
       </c>
     </row>
@@ -2910,14 +3073,31 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D15" s="5" t="inlineStr"/>
-      <c r="E15" s="5" t="inlineStr"/>
-      <c r="F15" s="5" t="inlineStr"/>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>山谷大地 ／ 新田</t>
+        <v>3</v>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>新田</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>山口</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>古川</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>運休</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>運休</t>
         </is>
       </c>
     </row>
@@ -2933,16 +3113,33 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>運休</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>船木智一</t>
+        </is>
+      </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>永井海里 ／ 徳留</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr"/>
+          <t>山谷大地</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>運休</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>古川</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
@@ -2956,20 +3153,33 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>船木智一 ／ 古川</t>
+          <t>山口</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>和田陽向太 ／ 山口</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
+          <t>新田</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>横山凌</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>徳留</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>運休</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
@@ -2987,18 +3197,27 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>船木智一 ／ 新田</t>
+          <t>徳留</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>和田陽向太 ／ 古川</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>山谷大地 ／ 徳留</t>
+          <t>古川</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>新田</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>運休</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>山口</t>
         </is>
       </c>
     </row>
@@ -3018,22 +3237,27 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>船木智一 ／ 徳留</t>
+          <t>古川</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>和田陽向太 ／ 新田</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>永井海里 ／ 古川</t>
+          <t>新田</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>運休</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>山谷大地 ／ 山口</t>
+          <t>山口</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>徳留</t>
         </is>
       </c>
     </row>
@@ -3049,16 +3273,33 @@
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D20" s="5" t="inlineStr"/>
-      <c r="E20" s="5" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>運休</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>運休</t>
+        </is>
+      </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>永井海里 ／ 山口</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr"/>
+          <t>徳留</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>山口</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>新田</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
@@ -3072,16 +3313,33 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D21" s="5" t="inlineStr"/>
-      <c r="E21" s="5" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>運休</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>運休</t>
+        </is>
+      </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>永井海里 ／ 徳留</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr"/>
+          <t>新田</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>古川</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>徳留</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
@@ -3095,20 +3353,33 @@
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>船木智一 ／ 新田</t>
+          <t>山口</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>和田陽向太 ／ 徳留</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
+          <t>古川</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>運休</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>新田</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>運休</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
@@ -3122,18 +3393,31 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D23" s="5" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>運休</t>
+        </is>
+      </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>和田陽向太 ／ 古川</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr"/>
+          <t>徳留</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>山口</t>
+        </is>
+      </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>山谷大地 ／ 山口</t>
+          <t>船木智一</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>古川</t>
         </is>
       </c>
     </row>
@@ -3149,14 +3433,31 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>山谷大地 ／ 古川</t>
+        <v>3</v>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>徳留</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>山口</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>古川</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>運休</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>運休</t>
         </is>
       </c>
     </row>
@@ -3176,18 +3477,27 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>船木智一 ／ 山口</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr"/>
+          <t>古川</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>運休</t>
+        </is>
+      </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>永井海里 ／ 新田</t>
+          <t>和田陽向太</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>山谷大地 ／ 徳留</t>
+          <t>徳留</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>新田</t>
         </is>
       </c>
     </row>
@@ -3207,20 +3517,29 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>船木智一 ／ 徳留</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>和田陽向太 ／ 古川</t>
+          <t>新田</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>運休</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>永井海里 ／ 新田</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr"/>
+          <t>徳留</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>古川</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>山口</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
@@ -3234,20 +3553,33 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>船木智一 ／ 新田</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr"/>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>永井海里 ／ 徳留</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr"/>
+          <t>新田</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>山口</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>運休</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>運休</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>永井海里</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
@@ -3261,18 +3593,31 @@
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D28" s="5" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>運休</t>
+        </is>
+      </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>和田陽向太 ／ 徳留</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="inlineStr"/>
+          <t>徳留</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>山口</t>
+        </is>
+      </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>山谷大地 ／ 新田</t>
+          <t>古川</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>新田</t>
         </is>
       </c>
     </row>
@@ -3288,18 +3633,31 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D29" s="5" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>運休</t>
+        </is>
+      </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>和田陽向太 ／ 山口</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr"/>
+          <t>新田</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>運休</t>
+        </is>
+      </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>山谷大地 ／ 古川</t>
+          <t>徳留</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>古川</t>
         </is>
       </c>
     </row>
@@ -3315,16 +3673,33 @@
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>船木智一 ／ 古川</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
+          <t>新田</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>古川</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>運休</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>運休</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>山口</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
@@ -3338,16 +3713,33 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D31" s="5" t="inlineStr"/>
-      <c r="E31" s="5" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>古川</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>運休</t>
+        </is>
+      </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>永井海里 ／ 新田</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr"/>
+          <t>徳留</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>山口</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>運休</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
@@ -3363,20 +3755,29 @@
       <c r="C32" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="D32" s="5" t="inlineStr"/>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>徳留</t>
+        </is>
+      </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>和田陽向太 ／ 新田</t>
+          <t>横山凌</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>永井海里 ／ 山口</t>
+          <t>古川</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>山谷大地 ／ 徳留</t>
+          <t>新田</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>運休</t>
         </is>
       </c>
     </row>
@@ -3395,7 +3796,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3420,11 +3821,13 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>平日の組数</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2</v>
+          <t>目標の平均出勤日数</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>24日</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -3483,7 +3886,7 @@
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>出勤日数・土日出勤</t>
+          <t>1人ごとの内訳</t>
         </is>
       </c>
     </row>
@@ -3495,7 +3898,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>出勤16日／土日7日／公休15日／最大3連勤</t>
+          <t>出勤24日／土日8日／公休7日／最大6連勤／助手席2日</t>
         </is>
       </c>
     </row>
@@ -3507,7 +3910,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>出勤16日／土日7日／公休15日／最大4連勤</t>
+          <t>出勤24日／土日8日／公休7日／最大6連勤／助手席2日</t>
         </is>
       </c>
     </row>
@@ -3519,7 +3922,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>出勤16日／土日8日／公休15日／最大3連勤</t>
+          <t>出勤23日／土日7日／公休8日／最大6連勤／助手席2日</t>
         </is>
       </c>
     </row>
@@ -3531,7 +3934,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>出勤16日／土日7日／公休15日／最大4連勤</t>
+          <t>出勤23日／土日7日／公休8日／最大6連勤／助手席2日</t>
         </is>
       </c>
     </row>
@@ -3543,7 +3946,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>出勤16日／土日7日／公休15日／最大3連勤</t>
+          <t>出勤25日／土日9日／公休6日／最大6連勤／助手席3日</t>
         </is>
       </c>
     </row>
@@ -3555,7 +3958,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>出勤20日／土日9日／公休11日／最大4連勤</t>
+          <t>出勤25日／土日9日／公休6日／最大6連勤</t>
         </is>
       </c>
     </row>
@@ -3567,7 +3970,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>出勤20日／土日9日／公休11日／最大4連勤</t>
+          <t>出勤25日／土日9日／公休6日／最大6連勤</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3982,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>出勤20日／土日9日／公休11日／最大4連勤</t>
+          <t>出勤23日／土日7日／公休8日／最大6連勤</t>
         </is>
       </c>
     </row>
@@ -3591,7 +3994,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>出勤20日／土日9日／公休11日／最大4連勤</t>
+          <t>出勤24日／土日8日／公休7日／最大6連勤</t>
         </is>
       </c>
     </row>
